--- a/Luban/Config/Datas/Levels/L11/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L11/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L11 W1/25; N=41; EHP=243.540000; normal:17x20,normal:18x21</t>
+          <t>L11 W1/25; N=41; EHP=538.465122; normal:17x20,normal:18x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L11 W2/25; N=47; EHP=292.329378; normal:17x24,normal:18x23</t>
+          <t>L11 W2/25; N=47; EHP=646.338073; normal:17x24,normal:18x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3504136,3504673,3504019,3504136,3504673,3504091,3504136,3504673,3504099,3504136,3504673,3504099,3504136,3504673,3504107,3504136,3504673,3504115,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504136,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144</t>
+          <t>3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504136,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144,3504144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L11 W3/25; N=53; EHP=364.687488; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x16,normal:18x17,swarm:84x14</t>
+          <t>L11 W3/25; N=53; EHP=865.715518; normal:17x16,normal:18x23,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3506136,3506673,3506019,3506136,3506673,3506019,3506136,3506673,3506091,3506136,3506673,3506099,3506136,3506673,3506107,3506136,3506673,3506107,3506136,3506673,3506115,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506136,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144</t>
+          <t>3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506136,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506136,3506136,3506136,3506136,3506136,3506136,3506136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L11 W4/25; N=59; EHP=467.478594; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x18,normal:18x18,swarm:84x16</t>
+          <t>L11 W4/25; N=59; EHP=1113.901026; normal:17x25,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3508136,3508673,3508019,3508668,3508136,3508673,3508091,3508668,3508136,3508673,3508091,3508668,3508136,3508673,3508099,3508868,3508136,3508673,3508107,3508868,3508136,3508673,3508107,3508868,3508136,3508673,3508115,3508988,3508136,3508673,3508115,3508988,3508136,3508673,3508988,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508144,3508673,3508144,3508673,3508144,3508673,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144</t>
+          <t>3508136,3508019,3508019,3508668,3508136,3508091,3508091,3508668,3508136,3508091,3508091,3508668,3508136,3508099,3508099,3508868,3508136,3508107,3508107,3508868,3508136,3508107,3508107,3508868,3508136,3508115,3508115,3508988,3508136,3508115,3508115,3508988,3508136,3508673,3508988,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508673,3508144,3508673,3508144,3508673,3508144,3508673,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144,3508144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L11 W5/25; N=65; EHP=887.047762; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x15,normal:18x15,medium:83x3,swarm:84x18,medium:108x3,medium:123x3</t>
+          <t>L11 W5/25; N=65; EHP=1987.147149; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x3,normal:17x15,normal:18x15,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3510136,3510673,3510242,3510019,3510668,3510136,3510673,3510242,3510019,3510668,3510136,3510673,3510466,3510091,3510668,3510136,3510673,3510466,3510091,3510868,3510136,3510673,3510514,3510099,3510868,3510136,3510673,3510514,3510099,3510868,3510136,3510673,3510786,3510107,3510868,3510136,3510673,3510786,3510115,3510988,3510136,3510673,3510115,3510988,3510136,3510673,3510988,3510136,3510673,3510136,3510673,3510136,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510144,3510144,3510144,3510144,3510144</t>
+          <t>3510136,3510019,3510242,3510019,3510668,3510136,3510019,3510242,3510019,3510668,3510136,3510091,3510466,3510091,3510668,3510136,3510091,3510466,3510091,3510868,3510136,3510099,3510514,3510099,3510868,3510136,3510099,3510514,3510099,3510868,3510136,3510107,3510786,3510107,3510868,3510136,3510115,3510786,3510115,3510988,3510136,3510115,3510115,3510988,3510136,3510673,3510988,3510136,3510673,3510136,3510673,3510136,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510673,3510144,3510144,3510144,3510144,3510144,3510144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L11 W6/25; N=71; EHP=905.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x12,fast:30x2,fast:58x2,fast:64x2,medium:83x3,swarm:84x19,fast:98x2,medium:108x4,medium:123x3</t>
+          <t>L11 W6/25; N=71; EHP=2028.568697; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x2,medium:83x3,medium:108x4,medium:123x3,normal:17x13,normal:18x12,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3512136,3512673,3512242,3512019,3512668,3512136,3512673,3512242,3512019,3512668,3512136,3512673,3512466,3512091,3512668,3512136,3512673,3512466,3512099,3512668,3512136,3512673,3512466,3512099,3512868,3512136,3512673,3512514,3512107,3512868,3512136,3512673,3512514,3512107,3512868,3512136,3512673,3512786,3512115,3512988,3512136,3512673,3512786,3512115,3512988,3512136,3512673,3512988,3512136,3512673,3512988,3512136,3512673,3512136,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512144,3512144,3512144,3512144,3512144</t>
+          <t>3512136,3512019,3512242,3512019,3512668,3512136,3512019,3512242,3512019,3512668,3512136,3512091,3512466,3512091,3512668,3512136,3512099,3512466,3512099,3512668,3512136,3512099,3512466,3512099,3512868,3512136,3512107,3512514,3512107,3512868,3512136,3512107,3512514,3512107,3512868,3512136,3512115,3512786,3512115,3512988,3512136,3512115,3512786,3512115,3512988,3512136,3512673,3512988,3512136,3512673,3512988,3512136,3512673,3512136,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512673,3512144,3512144,3512144,3512144,3512144,3512144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L11 W7/25; N=77; EHP=1027.092528; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x14,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x21,fast:98x2,medium:108x3,medium:123x4</t>
+          <t>L11 W7/25; N=77; EHP=2299.659635; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x2,medium:83x4,medium:108x3,medium:123x4,normal:17x13,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3514136,3514673,3514242,3514019,3514668,3514136,3514673,3514242,3514019,3514668,3514136,3514673,3514466,3514091,3514668,3514136,3514673,3514466,3514091,3514668,3514136,3514673,3514514,3514099,3514868,3514136,3514673,3514514,3514099,3514868,3514136,3514673,3514514,3514107,3514868,3514136,3514673,3514786,3514107,3514868,3514136,3514673,3514786,3514115,3514988,3514136,3514673,3514115,3514988,3514136,3514673,3514988,3514136,3514673,3514988,3514136,3514673,3514136,3514673,3514136,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514144,3514144,3514144,3514144,3514144</t>
+          <t>3514136,3514019,3514242,3514019,3514668,3514136,3514019,3514242,3514019,3514668,3514136,3514091,3514466,3514091,3514668,3514136,3514091,3514466,3514091,3514668,3514136,3514099,3514514,3514099,3514868,3514136,3514099,3514514,3514099,3514868,3514136,3514107,3514514,3514107,3514868,3514136,3514107,3514786,3514107,3514868,3514136,3514115,3514786,3514115,3514988,3514136,3514115,3514115,3514988,3514136,3514673,3514988,3514136,3514673,3514988,3514136,3514673,3514136,3514673,3514136,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514673,3514144,3514144,3514144,3514144,3514144,3514144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L11 W8/25; N=83; EHP=1322.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x2,fast:58x2,fast:64x3,medium:83x4,swarm:84x23,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L11 W8/25; N=83; EHP=2961.140397; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3516136,3516673,3516242,3516019,3516668,3516136,3516673,3516242,3516019,3516668,3516136,3516673,3516242,3516019,3516668,3516136,3516673,3516466,3516091,3516668,3516136,3516673,3516466,3516091,3516868,3516136,3516673,3516514,3516099,3516868,3516136,3516673,3516514,3516099,3516868,3516136,3516673,3516786,3516107,3516868,3516136,3516673,3516786,3516107,3516868,3516136,3516673,3516786,3516115,3516988,3516136,3516673,3516115,3516988,3516136,3516673,3516988,3516136,3516673,3516988,3516136,3516673,3516136,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516144,3516144,3516144,3516144,3516144,3516144</t>
+          <t>3516136,3516019,3516242,3516019,3516668,3516136,3516019,3516242,3516019,3516668,3516136,3516019,3516242,3516019,3516668,3516136,3516091,3516466,3516091,3516668,3516136,3516091,3516466,3516091,3516868,3516136,3516099,3516514,3516099,3516868,3516136,3516099,3516514,3516099,3516868,3516136,3516107,3516786,3516107,3516868,3516136,3516107,3516786,3516107,3516868,3516136,3516115,3516786,3516115,3516988,3516136,3516115,3516115,3516988,3516136,3516673,3516988,3516136,3516673,3516988,3516136,3516673,3516136,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516673,3516144,3516144,3516144,3516144,3516144,3516144,3516144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L11 W9/25; N=89; EHP=1688.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x16,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x24,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L11 W9/25; N=89; EHP=3782.129485; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x5,medium:123x4,normal:17x15,normal:18x16,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3518136,3518673,3518242,3518019,3518668,3518136,3518673,3518242,3518019,3518668,3518136,3518673,3518466,3518091,3518668,3518136,3518673,3518466,3518091,3518668,3518136,3518673,3518466,3518099,3518668,3518136,3518673,3518514,3518099,3518868,3518136,3518673,3518514,3518107,3518868,3518136,3518673,3518514,3518107,3518868,3518136,3518673,3518786,3518107,3518868,3518136,3518673,3518786,3518115,3518988,3518136,3518673,3518786,3518115,3518988,3518136,3518673,3518988,3518136,3518673,3518988,3518136,3518673,3518988,3518136,3518673,3518136,3518673,3518136,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518144,3518144,3518144,3518144,3518144,3518144</t>
+          <t>3518136,3518019,3518242,3518019,3518668,3518136,3518019,3518242,3518019,3518668,3518136,3518091,3518466,3518091,3518668,3518136,3518091,3518466,3518091,3518668,3518136,3518099,3518466,3518099,3518668,3518136,3518099,3518514,3518099,3518868,3518136,3518107,3518514,3518107,3518868,3518136,3518107,3518514,3518107,3518868,3518136,3518107,3518786,3518107,3518868,3518136,3518115,3518786,3518115,3518988,3518136,3518115,3518786,3518115,3518988,3518136,3518673,3518988,3518136,3518673,3518988,3518136,3518673,3518988,3518136,3518673,3518136,3518673,3518136,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518673,3518144,3518144,3518144,3518144,3518144,3518144,3518144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L11 W10/25; N=95; EHP=3115.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x5,swarm:84x26,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L11 W10/25; N=95; EHP=6973.332273; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x4,medium:123x5,normal:17x17,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3520136,3520673,3520242,3520019,3520668,3520253,3520136,3520673,3520242,3520019,3520668,3520325,3520136,3520673,3520242,3520091,3520668,3520541,3520136,3520673,3520466,3520091,3520668,3520541,3520136,3520673,3520466,3520091,3520668,3520565,3520136,3520673,3520466,3520099,3520868,3520565,3520136,3520673,3520514,3520099,3520868,3520645,3520136,3520673,3520514,3520107,3520868,3520693,3520136,3520673,3520514,3520107,3520868,3520709,3520136,3520673,3520786,3520115,3520868,3521021,3520136,3520673,3520786,3520115,3520988,3520136,3520673,3520786,3520115,3520988,3520144,3520673,3520988,3520144,3520673,3520988,3520144,3520673,3520988,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520673,3520673,3520673,3520673</t>
+          <t>3520136,3520019,3520242,3520019,3520668,3520253,3520136,3520019,3520242,3520019,3520668,3520325,3520136,3520091,3520242,3520091,3520668,3520541,3520136,3520091,3520466,3520091,3520668,3520541,3520136,3520091,3520466,3520091,3520668,3520565,3520136,3520099,3520466,3520099,3520868,3520565,3520136,3520099,3520514,3520099,3520868,3520645,3520136,3520107,3520514,3520107,3520868,3520693,3520136,3520107,3520514,3520107,3520868,3520709,3520136,3520115,3520786,3520115,3520868,3521021,3520136,3520115,3520786,3520115,3520988,3520136,3520115,3520786,3520115,3520988,3520144,3520673,3520988,3520144,3520673,3520988,3520144,3520673,3520988,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520144,3520673,3520673,3520673,3520673,3520673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L11 W11/25; N=101; EHP=3178.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x12,normal:18x12,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x28,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L11 W11/25; N=101; EHP=7106.608746; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x12,normal:18x12,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3522136,3522673,3522242,3522019,3522668,3522253,3522136,3522673,3522242,3522019,3522668,3522325,3522136,3522673,3522242,3522019,3522668,3522541,3522136,3522673,3522466,3522091,3522668,3522541,3522136,3522673,3522466,3522091,3522668,3522565,3522136,3522673,3522466,3522099,3522868,3522645,3522136,3522673,3522514,3522099,3522868,3522693,3522136,3522673,3522514,3522099,3522868,3522709,3522136,3522673,3522514,3522107,3522868,3522709,3522136,3522673,3522786,3522107,3522868,3523021,3522136,3522673,3522786,3522115,3522868,3522136,3522673,3522786,3522115,3522988,3522136,3522673,3522115,3522988,3522136,3522673,3522988,3522144,3522673,3522988,3522144,3522673,3522988,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522673,3522673</t>
+          <t>3522136,3522019,3522242,3522019,3522668,3522253,3522136,3522019,3522242,3522019,3522668,3522325,3522136,3522019,3522242,3522019,3522668,3522541,3522136,3522091,3522466,3522091,3522668,3522541,3522136,3522091,3522466,3522091,3522668,3522565,3522136,3522099,3522466,3522099,3522868,3522645,3522136,3522099,3522514,3522099,3522868,3522693,3522136,3522099,3522514,3522099,3522868,3522709,3522136,3522107,3522514,3522107,3522868,3522709,3522136,3522107,3522786,3522107,3522868,3523021,3522136,3522115,3522786,3522115,3522868,3522136,3522115,3522786,3522115,3522988,3522136,3522115,3522115,3522988,3522136,3522673,3522988,3522144,3522673,3522988,3522144,3522673,3522988,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522673,3522673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L11 W12/25; N=107; EHP=3289.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x2,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L11 W12/25; N=107; EHP=7357.044829; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x5,medium:108x6,medium:123x5,normal:17x14,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3524136,3524673,3524242,3524019,3524668,3524253,3524136,3524673,3524242,3524019,3524668,3524325,3524136,3524673,3524242,3524019,3524668,3524541,3524136,3524673,3524242,3524091,3524668,3524565,3524136,3524673,3524466,3524091,3524668,3524645,3524136,3524673,3524466,3524091,3524668,3524645,3524136,3524673,3524466,3524099,3524868,3524693,3524136,3524673,3524514,3524099,3524868,3524693,3524136,3524673,3524514,3524099,3524868,3524709,3524136,3524673,3524514,3524107,3524868,3524709,3524136,3524673,3524786,3524107,3524868,3525021,3524136,3524673,3524786,3524107,3524988,3524136,3524673,3524786,3524115,3524988,3524136,3524673,3524115,3524988,3524144,3524673,3524988,3524144,3524673,3524988,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524673,3524673,3524673</t>
+          <t>3524136,3524019,3524242,3524019,3524668,3524253,3524136,3524019,3524242,3524019,3524668,3524325,3524136,3524019,3524242,3524019,3524668,3524541,3524136,3524091,3524242,3524091,3524668,3524565,3524136,3524091,3524466,3524091,3524668,3524645,3524136,3524091,3524466,3524091,3524668,3524645,3524136,3524099,3524466,3524099,3524868,3524693,3524136,3524099,3524514,3524099,3524868,3524693,3524136,3524099,3524514,3524099,3524868,3524709,3524136,3524107,3524514,3524107,3524868,3524709,3524136,3524107,3524786,3524107,3524868,3525021,3524136,3524107,3524786,3524107,3524988,3524136,3524115,3524786,3524115,3524988,3524136,3524115,3524115,3524988,3524144,3524673,3524988,3524144,3524673,3524988,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524673,3524673,3524673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L11 W13/25; N=113; EHP=4013.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x14,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x31,heavy:86x2,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L11 W13/25; N=113; EHP=8978.973086; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x4,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x5,medium:123x5,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3526136,3526673,3526242,3526019,3526668,3526253,3526136,3526673,3526242,3526019,3526668,3526253,3526136,3526673,3526242,3526019,3526668,3526325,3526136,3526673,3526466,3526091,3526668,3526541,3526136,3526673,3526466,3526091,3526668,3526565,3526136,3526673,3526466,3526091,3526868,3526645,3526136,3526673,3526466,3526099,3526868,3526645,3526136,3526673,3526514,3526099,3526868,3526693,3526136,3526673,3526514,3526107,3526868,3526693,3526136,3526673,3526514,3526107,3526868,3526709,3526136,3526673,3526786,3526107,3526868,3527021,3526136,3526673,3526786,3526115,3526988,3526136,3526673,3526786,3526115,3526988,3526136,3526673,3526786,3526115,3526988,3526136,3526673,3526988,3526144,3526673,3526988,3526144,3526673,3526988,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526673,3526673,3526673</t>
+          <t>3526136,3526019,3526242,3526019,3526668,3526253,3526136,3526019,3526242,3526019,3526668,3526253,3526136,3526019,3526242,3526019,3526668,3526325,3526136,3526091,3526466,3526091,3526668,3526541,3526136,3526091,3526466,3526091,3526668,3526565,3526136,3526091,3526466,3526091,3526868,3526645,3526136,3526099,3526466,3526099,3526868,3526645,3526136,3526099,3526514,3526099,3526868,3526693,3526136,3526107,3526514,3526107,3526868,3526693,3526136,3526107,3526514,3526107,3526868,3526709,3526136,3526107,3526786,3526107,3526868,3527021,3526136,3526115,3526786,3526115,3526988,3526136,3526115,3526786,3526115,3526988,3526136,3526115,3526786,3526115,3526988,3526136,3526673,3526988,3526144,3526673,3526988,3526144,3526673,3526988,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526673,3526673,3526673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L11 W14/25; N=119; EHP=4843.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x3,heavy:31x2,heavy:40x1,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x33,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L11 W14/25; N=119; EHP=10829.962896; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3528136,3528673,3528242,3528019,3528668,3528253,3528542,3528136,3528673,3528242,3528019,3528668,3528253,3528136,3528673,3528242,3528019,3528668,3528325,3528136,3528673,3528242,3528091,3528668,3528325,3528136,3528673,3528466,3528091,3528668,3528541,3528136,3528673,3528466,3528091,3528668,3528565,3528136,3528673,3528466,3528099,3528868,3528645,3528136,3528673,3528466,3528099,3528868,3528693,3528136,3528673,3528514,3528099,3528868,3528693,3528136,3528673,3528514,3528107,3528868,3528709,3528136,3528673,3528514,3528107,3528868,3529021,3528136,3528673,3528514,3528107,3528868,3529021,3528136,3528673,3528786,3528115,3528988,3528136,3528673,3528786,3528115,3528988,3528144,3528673,3528786,3528115,3528988,3528144,3528673,3528988,3528144,3528673,3528988,3528144,3528673,3528988,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528673,3528673,3528673,3528673,3528673,3528673</t>
+          <t>3528136,3528019,3528242,3528019,3528668,3528253,3528542,3528136,3528019,3528242,3528019,3528668,3528253,3528136,3528019,3528242,3528019,3528668,3528325,3528136,3528091,3528242,3528091,3528668,3528325,3528136,3528091,3528466,3528091,3528668,3528541,3528136,3528091,3528466,3528091,3528668,3528565,3528136,3528099,3528466,3528099,3528868,3528645,3528136,3528099,3528466,3528099,3528868,3528693,3528136,3528099,3528514,3528099,3528868,3528693,3528136,3528107,3528514,3528107,3528868,3528709,3528136,3528107,3528514,3528107,3528868,3529021,3528136,3528107,3528514,3528107,3528868,3529021,3528136,3528115,3528786,3528115,3528988,3528136,3528115,3528786,3528115,3528988,3528144,3528115,3528786,3528115,3528988,3528144,3528673,3528988,3528144,3528673,3528988,3528144,3528673,3528988,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528673,3528673,3528673,3528673,3528673,3528673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L11 W15/25; N=125; EHP=8452.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L11 W15/25; N=125; EHP=18897.988839; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3530136,3530673,3530242,3530019,3530668,3530253,3530136,3530673,3530242,3530019,3530668,3530253,3530136,3530673,3530242,3530019,3530668,3530325,3530136,3530673,3530242,3530091,3530668,3530325,3530136,3530673,3530466,3530091,3530668,3530541,3530136,3530673,3530466,3530091,3530668,3530541,3530136,3530673,3530466,3530091,3530668,3530565,3530136,3530673,3530514,3530099,3530868,3530565,3530136,3530673,3530514,3530099,3530868,3530645,3530136,3530673,3530514,3530099,3530868,3530693,3530136,3530673,3530514,3530107,3530868,3530709,3530136,3530673,3530786,3530107,3530868,3531021,3530136,3530673,3530786,3530107,3530868,3531021,3530136,3530673,3530786,3530115,3530988,3530136,3530673,3530786,3530115,3530988,3530136,3530673,3530115,3530988,3530144,3530673,3530988,3530144,3530673,3530988,3530144,3530673,3530988,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530673,3530673,3530673,3530673</t>
+          <t>3530136,3530019,3530242,3530019,3530668,3530253,3530136,3530019,3530242,3530019,3530668,3530253,3530136,3530019,3530242,3530019,3530668,3530325,3530136,3530091,3530242,3530091,3530668,3530325,3530136,3530091,3530466,3530091,3530668,3530541,3530136,3530091,3530466,3530091,3530668,3530541,3530136,3530091,3530466,3530091,3530668,3530565,3530136,3530099,3530514,3530099,3530868,3530565,3530136,3530099,3530514,3530099,3530868,3530645,3530136,3530099,3530514,3530099,3530868,3530693,3530136,3530107,3530514,3530107,3530868,3530709,3530136,3530107,3530786,3530107,3530868,3531021,3530136,3530107,3530786,3530107,3530868,3531021,3530136,3530115,3530786,3530115,3530988,3530136,3530115,3530786,3530115,3530988,3530136,3530115,3530115,3530988,3530144,3530673,3530988,3530144,3530673,3530988,3530144,3530673,3530988,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530144,3530673,3530673,3530673,3530673,3530673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L11 W16/25; N=131; EHP=8622.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x36,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L11 W16/25; N=131; EHP=19287.038819; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3532136,3532673,3532242,3532019,3532668,3532253,3532136,3532673,3532242,3532019,3532668,3532325,3532136,3532673,3532242,3532019,3532668,3532325,3532136,3532673,3532242,3532091,3532668,3532541,3532136,3532673,3532466,3532091,3532668,3532541,3532136,3532673,3532466,3532091,3532668,3532565,3532136,3532673,3532466,3532099,3532868,3532565,3532136,3532673,3532466,3532099,3532868,3532645,3532136,3532673,3532514,3532099,3532868,3532693,3532136,3532673,3532514,3532107,3532868,3532709,3532136,3532673,3532514,3532107,3532868,3532709,3532136,3532673,3532514,3532107,3532868,3533021,3532136,3532673,3532786,3532115,3532868,3533021,3532136,3532673,3532786,3532115,3532988,3532136,3532673,3532786,3532115,3532988,3532136,3532673,3532786,3532115,3532988,3532136,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532673,3532673,3532673,3532673</t>
+          <t>3532136,3532019,3532242,3532019,3532668,3532253,3532136,3532019,3532242,3532019,3532668,3532325,3532136,3532019,3532242,3532019,3532668,3532325,3532136,3532091,3532242,3532091,3532668,3532541,3532136,3532091,3532466,3532091,3532668,3532541,3532136,3532091,3532466,3532091,3532668,3532565,3532136,3532099,3532466,3532099,3532868,3532565,3532136,3532099,3532466,3532099,3532868,3532645,3532136,3532099,3532514,3532099,3532868,3532693,3532136,3532107,3532514,3532107,3532868,3532709,3532136,3532107,3532514,3532107,3532868,3532709,3532136,3532107,3532514,3532107,3532868,3533021,3532136,3532115,3532786,3532115,3532868,3533021,3532136,3532115,3532786,3532115,3532988,3532136,3532115,3532786,3532115,3532988,3532136,3532115,3532786,3532115,3532988,3532136,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532988,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673,3532673,3532673,3532673,3532673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L11 W17/25; N=137; EHP=8795.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x38,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L11 W17/25; N=137; EHP=19664.631414; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3534136,3534673,3534242,3534019,3534668,3534253,3534136,3534673,3534242,3534019,3534668,3534325,3534136,3534673,3534242,3534019,3534668,3534541,3534136,3534673,3534242,3534019,3534668,3534541,3534136,3534673,3534466,3534091,3534668,3534565,3534136,3534673,3534466,3534091,3534668,3534565,3534136,3534673,3534466,3534091,3534668,3534645,3534136,3534673,3534466,3534099,3534868,3534645,3534136,3534673,3534514,3534099,3534868,3534693,3534136,3534673,3534514,3534099,3534868,3534693,3534136,3534673,3534514,3534099,3534868,3534709,3534136,3534673,3534514,3534107,3534868,3534709,3534136,3534673,3534786,3534107,3534868,3535021,3534136,3534673,3534786,3534107,3534868,3535021,3534136,3534673,3534786,3534115,3534988,3534136,3534673,3534786,3534115,3534988,3534136,3534673,3534786,3534115,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534673,3534673,3534673,3534673,3534673,3534673</t>
+          <t>3534136,3534019,3534242,3534019,3534668,3534253,3534136,3534019,3534242,3534019,3534668,3534325,3534136,3534019,3534242,3534019,3534668,3534541,3534136,3534019,3534242,3534019,3534668,3534541,3534136,3534091,3534466,3534091,3534668,3534565,3534136,3534091,3534466,3534091,3534668,3534565,3534136,3534091,3534466,3534091,3534668,3534645,3534136,3534099,3534466,3534099,3534868,3534645,3534136,3534099,3534514,3534099,3534868,3534693,3534136,3534099,3534514,3534099,3534868,3534693,3534136,3534099,3534514,3534099,3534868,3534709,3534136,3534107,3534514,3534107,3534868,3534709,3534136,3534107,3534786,3534107,3534868,3535021,3534136,3534107,3534786,3534107,3534868,3535021,3534136,3534115,3534786,3534115,3534988,3534136,3534115,3534786,3534115,3534988,3534136,3534115,3534786,3534115,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534988,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534673,3534673,3534673,3534673,3534673,3534673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L11 W18/25; N=143; EHP=9398.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L11 W18/25; N=143; EHP=21016.620802; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3536136,3536673,3536242,3536019,3536668,3536253,3536136,3536673,3536242,3536019,3536668,3536253,3536136,3536673,3536242,3536019,3536668,3536325,3536136,3536673,3536242,3536019,3536668,3536541,3536136,3536673,3536466,3536091,3536668,3536541,3536136,3536673,3536466,3536091,3536668,3536565,3536136,3536673,3536466,3536091,3536668,3536565,3536136,3536673,3536466,3536091,3536668,3536645,3536136,3536673,3536466,3536099,3536868,3536645,3536136,3536673,3536514,3536099,3536868,3536693,3536136,3536673,3536514,3536099,3536868,3536693,3536136,3536673,3536514,3536107,3536868,3536709,3536136,3536673,3536514,3536107,3536868,3536709,3536136,3536673,3536786,3536107,3536868,3537021,3536136,3536673,3536786,3536107,3536868,3536136,3536673,3536786,3536115,3536988,3536136,3536673,3536786,3536115,3536988,3536136,3536673,3536115,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536673,3536673,3536673,3536673</t>
+          <t>3536136,3536019,3536242,3536019,3536668,3536253,3536136,3536019,3536242,3536019,3536668,3536253,3536136,3536019,3536242,3536019,3536668,3536325,3536136,3536019,3536242,3536019,3536668,3536541,3536136,3536091,3536466,3536091,3536668,3536541,3536136,3536091,3536466,3536091,3536668,3536565,3536136,3536091,3536466,3536091,3536668,3536565,3536136,3536091,3536466,3536091,3536668,3536645,3536136,3536099,3536466,3536099,3536868,3536645,3536136,3536099,3536514,3536099,3536868,3536693,3536136,3536099,3536514,3536099,3536868,3536693,3536136,3536107,3536514,3536107,3536868,3536709,3536136,3536107,3536514,3536107,3536868,3536709,3536136,3536107,3536786,3536107,3536868,3537021,3536136,3536107,3536786,3536107,3536868,3536136,3536115,3536786,3536115,3536988,3536136,3536115,3536786,3536115,3536988,3536136,3536115,3536115,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536988,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536673,3536673,3536673,3536673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L11 W19/25; N=149; EHP=10884.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x19,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L11 W19/25; N=149; EHP=24344.986790; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x19,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3538136,3538673,3538242,3538019,3538668,3538253,3538542,3538136,3538673,3538242,3538019,3538668,3538253,3538136,3538673,3538242,3538019,3538668,3538325,3538136,3538673,3538242,3538091,3538668,3538325,3538136,3538673,3538242,3538091,3538668,3538541,3538136,3538673,3538466,3538091,3538668,3538541,3538136,3538673,3538466,3538091,3538668,3538565,3538136,3538673,3538466,3538099,3538868,3538645,3538136,3538673,3538466,3538099,3538868,3538645,3538136,3538673,3538514,3538099,3538868,3538693,3538136,3538673,3538514,3538099,3538868,3538693,3538136,3538673,3538514,3538107,3538868,3538709,3538136,3538673,3538514,3538107,3538868,3538709,3538136,3538673,3538514,3538107,3538868,3539021,3538136,3538673,3538786,3538107,3538868,3539021,3538136,3538673,3538786,3538115,3538988,3538136,3538673,3538786,3538115,3538988,3538136,3538673,3538786,3538115,3538988,3538144,3538673,3538115,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538673,3538673,3538673,3538673,3538673,3538673,3538673</t>
+          <t>3538136,3538019,3538242,3538019,3538668,3538253,3538542,3538136,3538019,3538242,3538019,3538668,3538253,3538136,3538019,3538242,3538019,3538668,3538325,3538136,3538091,3538242,3538091,3538668,3538325,3538136,3538091,3538242,3538091,3538668,3538541,3538136,3538091,3538466,3538091,3538668,3538541,3538136,3538091,3538466,3538091,3538668,3538565,3538136,3538099,3538466,3538099,3538868,3538645,3538136,3538099,3538466,3538099,3538868,3538645,3538136,3538099,3538514,3538099,3538868,3538693,3538136,3538099,3538514,3538099,3538868,3538693,3538136,3538107,3538514,3538107,3538868,3538709,3538136,3538107,3538514,3538107,3538868,3538709,3538136,3538107,3538514,3538107,3538868,3539021,3538136,3538107,3538786,3538107,3538868,3539021,3538136,3538115,3538786,3538115,3538988,3538136,3538115,3538786,3538115,3538988,3538136,3538115,3538786,3538115,3538988,3538144,3538115,3538115,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538988,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538673,3538673,3538673,3538673,3538673,3538673,3538673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L11 W20/25; N=155; EHP=18277.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,elite:67x1,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L11 W20/25; N=155; EHP=40876.489038; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x18,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017505,10017514,10017507,10048570,10017513,10017508,10017505,10017514,10017507,10048570,10017513,10017508,10017505,10017514,10017507,10048570,10017513,10017509,10017505,10017514,10017507,10048570,10017513,10017509,10017505,10017514,10017507,10017502,10017513,10045164,10017505,10017514,10017510,10017502,10017513,10045164,10017505,10017514,10017510,10017502,10017513,10045165,10017505,10017514,10017510,10017502,10017513,10045165,10017505,10017514,10017510,10048571,10017518,10017512,10017505,10017514,10017510,10048571,10017518,10017512,10017505,10017514,10017511,10048571,10017518,10017515,10017505,10017514,10017511,10048571,10017518,10017515,10017505,10017514,10017511,10017503,10017518,10017516,10017505,10017514,10017511,10017503,10017518,10017516,10017505,10017514,10017517,10017503,10017518,10017520,10017505,10017514,10017517,10017504,10017518,10017520,10017505,10017514,10017517,10017504,10017519,10017505,10017514,10017517,10017504,10017519,10017505,10017514,10017517,10017504,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017514,10017514,10017514,10017514,10017514,10017514,10017514</t>
+          <t>10017505,10048570,10017507,10048570,10017513,10017508,10017505,10048570,10017507,10048570,10017513,10017508,10017505,10048570,10017507,10048570,10017513,10017509,10017505,10048570,10017507,10048570,10017513,10017509,10017505,10017502,10017507,10017502,10017513,10045164,10017505,10017502,10017510,10017502,10017513,10045164,10017505,10017502,10017510,10017502,10017513,10045165,10017505,10017502,10017510,10017502,10017513,10045165,10017505,10048571,10017510,10048571,10017518,10017512,10017505,10048571,10017510,10048571,10017518,10017512,10017505,10048571,10017511,10048571,10017518,10017515,10017505,10048571,10017511,10048571,10017518,10017515,10017505,10017503,10017511,10017503,10017518,10017516,10017505,10017503,10017511,10017503,10017518,10017516,10017505,10017503,10017517,10017503,10017518,10017520,10017505,10017504,10017517,10017504,10017518,10017520,10017505,10017504,10017517,10017504,10017519,10017505,10017504,10017517,10017504,10017519,10017505,10017504,10017517,10017504,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017519,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017506,10017514,10017514,10017514,10017514,10017514,10017514,10017514,10017514</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L11 W21/25; N=161; EHP=18643.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L11 W21/25; N=161; EHP=41685.845942; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017524,10017535,10017526,10048572,10017534,10017527,10017524,10017535,10017526,10048572,10017534,10017527,10017524,10017535,10017526,10048572,10017534,10017528,10017524,10017535,10017526,10048572,10017534,10017528,10017524,10017535,10017526,10017521,10017534,10017531,10017524,10017535,10017529,10017521,10017534,10017531,10017524,10017535,10017529,10017521,10017534,10017532,10017524,10017535,10017529,10017521,10017534,10017532,10017524,10017535,10017529,10048573,10017534,10017533,10017524,10017535,10017529,10048573,10017538,10017533,10017524,10017535,10017530,10048573,10017538,10017536,10017524,10017535,10017530,10048573,10017538,10017536,10017524,10017535,10017530,10017522,10017538,10045166,10017524,10017535,10017530,10017522,10017538,10045166,10017524,10017535,10017530,10017522,10017538,10017540,10017524,10017535,10017537,10017522,10017538,10017540,10017524,10017535,10017537,10017523,10017538,10017524,10017535,10017537,10017523,10017539,10017524,10017535,10017537,10017523,10017539,10017524,10017535,10017537,10017523,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017535,10017535,10017535,10017535,10017535,10017535</t>
+          <t>10017524,10048572,10017526,10048572,10017534,10017527,10017524,10048572,10017526,10048572,10017534,10017527,10017524,10048572,10017526,10048572,10017534,10017528,10017524,10048572,10017526,10048572,10017534,10017528,10017524,10017521,10017526,10017521,10017534,10017531,10017524,10017521,10017529,10017521,10017534,10017531,10017524,10017521,10017529,10017521,10017534,10017532,10017524,10017521,10017529,10017521,10017534,10017532,10017524,10048573,10017529,10048573,10017534,10017533,10017524,10048573,10017529,10048573,10017538,10017533,10017524,10048573,10017530,10048573,10017538,10017536,10017524,10048573,10017530,10048573,10017538,10017536,10017524,10017522,10017530,10017522,10017538,10045166,10017524,10017522,10017530,10017522,10017538,10045166,10017524,10017522,10017530,10017522,10017538,10017540,10017524,10017522,10017537,10017522,10017538,10017540,10017524,10017523,10017537,10017523,10017538,10017524,10017523,10017537,10017523,10017539,10017524,10017523,10017537,10017523,10017539,10017524,10017523,10017537,10017523,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017539,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017525,10017535,10017535,10017535,10017535,10017535,10017535,10017535</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L11 W22/25; N=167; EHP=19016.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L11 W22/25; N=167; EHP=42528.614653; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017544,10017554,10017546,10048574,10017553,10017547,10017544,10017554,10017546,10048574,10017553,10017547,10017544,10017554,10017546,10048574,10017553,10017548,10017544,10017554,10017546,10048574,10017553,10017548,10017544,10017554,10017546,10017541,10017553,10017551,10017544,10017554,10017549,10017541,10017553,10017551,10017544,10017554,10017549,10017541,10017553,10017552,10017544,10017554,10017549,10017541,10017553,10017552,10017544,10017554,10017549,10048575,10017558,10045167,10017544,10017554,10017549,10048575,10017558,10045167,10017544,10017554,10017550,10048575,10017558,10017555,10017544,10017554,10017550,10048575,10017558,10017555,10017544,10017554,10017550,10048575,10017558,10017555,10017544,10017554,10017550,10017542,10017558,10017556,10017544,10017554,10017550,10017542,10017558,10017556,10017544,10017554,10017557,10017542,10017558,10017560,10017544,10017554,10017557,10017542,10017559,10017560,10017544,10017554,10017557,10017543,10017559,10017544,10017554,10017557,10017543,10017559,10017544,10017554,10017557,10017543,10017559,10017544,10017554,10017543,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017554,10017554,10017554,10017554,10017554,10017554</t>
+          <t>10017544,10048574,10017546,10048574,10017553,10017547,10017544,10048574,10017546,10048574,10017553,10017547,10017544,10048574,10017546,10048574,10017553,10017548,10017544,10048574,10017546,10048574,10017553,10017548,10017544,10017541,10017546,10017541,10017553,10017551,10017544,10017541,10017549,10017541,10017553,10017551,10017544,10017541,10017549,10017541,10017553,10017552,10017544,10017541,10017549,10017541,10017553,10017552,10017544,10048575,10017549,10048575,10017558,10045167,10017544,10048575,10017549,10048575,10017558,10045167,10017544,10048575,10017550,10048575,10017558,10017555,10017544,10048575,10017550,10048575,10017558,10017555,10017544,10048575,10017550,10048575,10017558,10017555,10017544,10017542,10017550,10017542,10017558,10017556,10017544,10017542,10017550,10017542,10017558,10017556,10017544,10017542,10017557,10017542,10017558,10017560,10017544,10017542,10017557,10017542,10017559,10017560,10017544,10017543,10017557,10017543,10017559,10017544,10017543,10017557,10017543,10017559,10017544,10017543,10017557,10017543,10017559,10017544,10017543,10017543,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017559,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017545,10017554,10017554,10017554,10017554,10017554,10017554,10017554</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L11 W23/25; N=173; EHP=19397.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x48,heavy:86x3,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L11 W23/25; N=173; EHP=43388.220153; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017564,10017575,10017566,10048576,10017574,10017567,10017564,10017575,10017566,10048576,10017574,10017567,10017564,10017575,10017566,10048576,10017574,10017567,10017564,10017575,10017566,10048576,10017574,10017568,10017564,10017575,10017566,10048576,10017574,10017568,10017564,10017575,10017569,10017561,10017574,10017571,10017564,10017575,10017569,10017561,10017574,10017571,10017564,10017575,10017569,10017561,10017574,10017572,10017564,10017575,10017569,10017561,10017574,10017572,10017564,10017575,10017569,10048577,10017578,10017573,10017564,10017575,10017570,10048577,10017578,10017573,10017564,10017575,10017570,10048577,10017578,10045168,10017564,10017575,10017570,10048577,10017578,10045168,10017564,10017575,10017570,10017562,10017578,10017576,10017564,10017575,10017570,10017562,10017578,10017576,10017564,10017575,10017570,10017562,10017578,10017580,10017564,10017575,10017577,10017562,10017578,10017580,10017564,10017575,10017577,10017563,10017578,10017564,10017575,10017577,10017563,10017579,10017564,10017575,10017577,10017563,10017579,10017564,10017575,10017577,10017563,10017579,10017564,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017575,10017575,10017575,10017575,10017575,10017575</t>
+          <t>10017564,10048576,10017566,10048576,10017574,10017567,10017564,10048576,10017566,10048576,10017574,10017567,10017564,10048576,10017566,10048576,10017574,10017567,10017564,10048576,10017566,10048576,10017574,10017568,10017564,10048576,10017566,10048576,10017574,10017568,10017564,10017561,10017569,10017561,10017574,10017571,10017564,10017561,10017569,10017561,10017574,10017571,10017564,10017561,10017569,10017561,10017574,10017572,10017564,10017561,10017569,10017561,10017574,10017572,10017564,10048577,10017569,10048577,10017578,10017573,10017564,10048577,10017570,10048577,10017578,10017573,10017564,10048577,10017570,10048577,10017578,10045168,10017564,10048577,10017570,10048577,10017578,10045168,10017564,10017562,10017570,10017562,10017578,10017576,10017564,10017562,10017570,10017562,10017578,10017576,10017564,10017562,10017570,10017562,10017578,10017580,10017564,10017562,10017577,10017562,10017578,10017580,10017564,10017563,10017577,10017563,10017578,10017564,10017563,10017577,10017563,10017579,10017564,10017563,10017577,10017563,10017579,10017564,10017563,10017577,10017563,10017579,10017564,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017579,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017565,10017575,10017575,10017575,10017575,10017575,10017575,10017575</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L11 W24/25; N=179; EHP=20770.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x3,heavy:40x2,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L11 W24/25; N=179; EHP=46442.470656; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017584,10017594,10017586,10048578,10017593,10045169,10017599,10017584,10017594,10017586,10048578,10017593,10045169,10017584,10017594,10017586,10048578,10017593,10017587,10017584,10017594,10017586,10048578,10017593,10017587,10017584,10017594,10017586,10017581,10017593,10017587,10017584,10017594,10017586,10017581,10017593,10017590,10017584,10017594,10017588,10017581,10017593,10017590,10017584,10017594,10017588,10017581,10017593,10017591,10017584,10017594,10017588,10017581,10017593,10017591,10017584,10017594,10017588,10048579,10017598,10017592,10017584,10017594,10017588,10048579,10017598,10017592,10017584,10017594,10017589,10048579,10017598,10017595,10017584,10017594,10017589,10048579,10017598,10017595,10017584,10017594,10017589,10017582,10017598,10017596,10017584,10017594,10017589,10017582,10017598,10017596,10017584,10017594,10017589,10017582,10017598,10017601,10017584,10017594,10017597,10017582,10017598,10017601,10017584,10017594,10017597,10017582,10017598,10017601,10017584,10017594,10017597,10017583,10017600,10017584,10017594,10017597,10017583,10017600,10017584,10017594,10017597,10017583,10017600,10017584,10017594,10017597,10017583,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017594,10017594,10017594,10017594,10017594,10017594,10017594</t>
+          <t>10017584,10048578,10017586,10048578,10017593,10045169,10017599,10017584,10048578,10017586,10048578,10017593,10045169,10017584,10048578,10017586,10048578,10017593,10017587,10017584,10048578,10017586,10048578,10017593,10017587,10017584,10017581,10017586,10017581,10017593,10017587,10017584,10017581,10017586,10017581,10017593,10017590,10017584,10017581,10017588,10017581,10017593,10017590,10017584,10017581,10017588,10017581,10017593,10017591,10017584,10017581,10017588,10017581,10017593,10017591,10017584,10048579,10017588,10048579,10017598,10017592,10017584,10048579,10017588,10048579,10017598,10017592,10017584,10048579,10017589,10048579,10017598,10017595,10017584,10048579,10017589,10048579,10017598,10017595,10017584,10017582,10017589,10017582,10017598,10017596,10017584,10017582,10017589,10017582,10017598,10017596,10017584,10017582,10017589,10017582,10017598,10017601,10017584,10017582,10017597,10017582,10017598,10017601,10017584,10017582,10017597,10017582,10017598,10017601,10017584,10017583,10017597,10017583,10017600,10017584,10017583,10017597,10017583,10017600,10017584,10017583,10017597,10017583,10017600,10017584,10017583,10017597,10017583,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017600,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017585,10017594,10017594,10017594,10017594,10017594,10017594,10017594,10017594</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L11 W25/25; N=185; EHP=41458.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,elite:123x1,medium:123x9,heavy:127x3</t>
+          <t>L11 W25/25; N=185; EHP=92691.940277; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L11/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L11/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>239</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>232</v>
+        <v>330</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>225</v>
+        <v>360</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>183</v>
+        <v>360</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>169</v>
+        <v>290</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
